--- a/public/documents/pieces-defense/RF-anomalies-tva.xlsx
+++ b/public/documents/pieces-defense/RF-anomalies-tva.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Ventilation TVA par exercice" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Coherence par famille" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Ecarts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Reconciliation caisse-compta" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1092,4 +1093,244 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Exercice</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Base 10 % reconstituee (caisse)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Compta 706300</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Ecart 10 %</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Base 20 % reconstituee (caisse)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Compta 706000</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Base 20 % brute (fisc)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>TVA caisse</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>TVA compta 445710</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Ecart TVA</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>CA TTC caisse</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>CA TTC compta</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Ecart CA</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dont pourboire 706800</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ex. clos 31/03/2023</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>296111</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>296105.87</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>5.130000000004657</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>64708.3</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>64712.51</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>-11645.01</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>42552.76</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>42614.45</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>-61.68999999999505</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>403370.42</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>404030.87</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>-660.4500000000116</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>598.04</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ex. clos 31/03/2024</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>319174.4</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>319179.31</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>-4.909999999974389</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>72413.2</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>72416.55</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>-1680.08</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>46400.08</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>46464.79</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>-64.70999999999913</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>437992.92</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>438658.43</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>-665.5100000000093</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>597.75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ex. clos 31/03/2025</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>318522</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>318345.43</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>176.570000000007</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>70372.14999999999</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>70517.47</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>572.55</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>45926.63</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>46005.45</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>-78.81999999999971</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>434827.86</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>435524.92</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>-697.0599999999977</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>656.5700000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/public/documents/pieces-defense/RF-anomalies-tva.xlsx
+++ b/public/documents/pieces-defense/RF-anomalies-tva.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Coherence par famille" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Ecarts" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Reconciliation caisse-compta" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Exemple ticket base negative" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1101,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1110,14 +1111,16 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1168,7 +1171,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Ecart TVA</t>
+          <t>Ecart TVA (caisse - compta)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -1178,17 +1181,27 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>CA TTC annexe G (fisc)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>CA TTC compta</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Ecart CA</t>
-        </is>
-      </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>Ecart CA (caisse - compta)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>dont pourboire 706800</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Solde arrondis (compta - caisse - pourboire)</t>
         </is>
       </c>
     </row>
@@ -1229,13 +1242,19 @@
         <v>403370.42</v>
       </c>
       <c r="L2" s="2" t="n">
+        <v>403324.72</v>
+      </c>
+      <c r="M2" s="2" t="n">
         <v>404030.87</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="N2" s="2" t="n">
         <v>-660.4500000000116</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="O2" s="2" t="n">
         <v>598.04</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>62.41000000001168</v>
       </c>
     </row>
     <row r="3">
@@ -1275,13 +1294,19 @@
         <v>437992.92</v>
       </c>
       <c r="L3" s="2" t="n">
+        <v>437881.12</v>
+      </c>
+      <c r="M3" s="2" t="n">
         <v>438658.43</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="N3" s="2" t="n">
         <v>-665.5100000000093</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="O3" s="2" t="n">
         <v>597.75</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>67.76000000000931</v>
       </c>
     </row>
     <row r="4">
@@ -1321,16 +1346,138 @@
         <v>434827.86</v>
       </c>
       <c r="L4" s="2" t="n">
+        <v>434709.26</v>
+      </c>
+      <c r="M4" s="2" t="n">
         <v>435524.92</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="N4" s="2" t="n">
         <v>-697.0599999999977</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="O4" s="2" t="n">
         <v>656.5700000000001</v>
       </c>
+      <c r="P4" s="2" t="n">
+        <v>40.48999999999762</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Methode : base = TVA collectee (tax_amount, annexe G) / taux. TVA caisse = somme des tax_amount. CA TTC caisse = somme des tot_ttc par ticket distinct. Comptabilite (706300=HT 10 %, 706000=HT 20 %, 445710=TVA, 706800=pourboire) : chiffres reproduits par le service p. 26 du rapport. Droit applicable : CGI art. 279 m (10 %) https://www.legifrance.gouv.fr/codes/article_lc/LEGIARTI000028416998/2014-01-01 ; CGI art. 278 (20 %) https://www.legifrance.gouv.fr/codes/id/LEGISCTA000006191854 ; BOFiP https://bofip.impots.gouv.fr/bofip/256-PGP.html.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A5:P5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ticket n° 2 du 14/04/2022 : TTC 20,90 €, TVA totale 2,30 €</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Ligne de taux</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Champ base HT du fichier (brut)</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>TVA reellement collectee (tax_amount)</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Base reconstituee (TVA / taux)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ligne 10 %</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ligne 20 %</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>-14.8</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL ticket</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Lecture : le champ « base HT 20 % » de l'export vaut -14,80 € (residu non additif), mais la TVA reellement collectee au taux de 20 % est +0,87 € (base reelle 4,35 €). La TVA par ligne est toujours positive ; sa somme (1,43 + 0,87 = 2,30 €) egale la TVA totale du ticket. Effet sur la TVA et le CA : nul. Ce cas concerne 8526 lignes sur 29588 (28,8 %).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A7:D7"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/documents/pieces-defense/RF-anomalies-tva.xlsx
+++ b/public/documents/pieces-defense/RF-anomalies-tva.xlsx
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14.3</v>
+        <v>5.7</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>1.43</v>
@@ -1458,19 +1458,23 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>TOTAL ticket</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr"/>
+          <t>TOTAL ticket (HT reel = 18,60 €)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>-9.1</v>
+      </c>
       <c r="C6" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="D6" s="2" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>18.65</v>
+      </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Lecture : le champ « base HT 20 % » de l'export vaut -14,80 € (residu non additif), mais la TVA reellement collectee au taux de 20 % est +0,87 € (base reelle 4,35 €). La TVA par ligne est toujours positive ; sa somme (1,43 + 0,87 = 2,30 €) egale la TVA totale du ticket. Effet sur la TVA et le CA : nul. Ce cas concerne 8526 lignes sur 29588 (28,8 %).</t>
+          <t>Lecture : les deux champs « base HT » bruts du fichier (5,70 € et -14,80 €) s'additionnent a -9,10 €, montant absurde pour une vente de 20,90 € (HT reel = 20,90 - 2,30 = 18,60 €) : la colonne « base » de l'export est non additive, donc non fiable. Les bases reconstituees base = TVA / taux (14,30 € + 4,35 €) redonnent 18,65 €, soit le HT reel a 5 centimes pres (arrondi de la TVA de chaque ligne). La TVA par ligne est toujours positive ; sa somme (1,43 + 0,87 = 2,30 €) egale la TVA totale du ticket. Effet sur la TVA et le CA : nul. Ce cas concerne 8526 lignes sur 29588 (28,8 %), toutes sur des tickets a deux taux.</t>
         </is>
       </c>
     </row>
